--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendratyler\Documents\dataanalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35056393-4C98-4C1E-A887-4707723294FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14A2A70-1E41-4D0C-BB5A-6D6A770FE25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="167">
   <si>
     <t>Event ID</t>
   </si>
@@ -407,9 +407,6 @@
     <t>GallDst_FL</t>
   </si>
   <si>
-    <t>4th table?</t>
-  </si>
-  <si>
     <t>u0865</t>
   </si>
   <si>
@@ -446,18 +443,9 @@
     <t>Zip</t>
   </si>
   <si>
-    <t>Contact Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
-    <t>Downtown Convention Ctr</t>
-  </si>
-  <si>
     <t>1847 Sunset Blvd</t>
   </si>
   <si>
@@ -494,18 +482,6 @@
     <t>Patricia Anderson</t>
   </si>
   <si>
-    <t>Employee Tables</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Mananger Email</t>
-  </si>
-  <si>
-    <t>U0156</t>
-  </si>
-  <si>
     <t>Categories Table</t>
   </si>
   <si>
@@ -537,6 +513,47 @@
   </si>
   <si>
     <t>Confrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunset Poetry Reading </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Manangers </t>
+  </si>
+  <si>
+    <t>Event Manangers Name</t>
+  </si>
+  <si>
+    <t>Event Mananger Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Mananger ID </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Numers of Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>4th table:</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1780,7 +1797,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>39</v>
@@ -2110,7 +2127,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>39</v>
@@ -2210,7 +2227,7 @@
         <v>100</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2262,13 +2279,13 @@
         <v>103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -2286,7 +2303,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
@@ -2301,7 +2318,7 @@
         <v>116</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -2319,7 +2336,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>7</v>
@@ -2334,7 +2351,7 @@
         <v>115</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -2352,7 +2369,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>10</v>
@@ -2385,7 +2402,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>14</v>
@@ -2397,10 +2414,10 @@
         <v>46157</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -2418,22 +2435,22 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D23" s="4">
-        <v>46215</v>
+        <v>46109</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2450,12 +2467,24 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="A24" s="3">
+        <v>106</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46130</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -2471,12 +2500,24 @@
       <c r="S24" s="3"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="A25" s="3">
+        <v>107</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46144</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -2492,12 +2533,24 @@
       <c r="S25" s="3"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="A26" s="3">
+        <v>108</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="4">
+        <v>46181</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -2512,328 +2565,747 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>109</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46215</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>110</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="4">
+        <v>46102</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>111</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B37" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
+      <c r="B39" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C39" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="D39" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E39" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="G39" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G35" s="9" t="s">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="D40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" s="8">
+        <v>90026</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="D41" s="8" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="E41" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="8">
+        <v>78741</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" s="8">
+        <v>90046</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="8">
+        <v>60616</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" s="3">
+        <v>10011</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="3">
+        <v>60616</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" s="3">
+        <v>97214</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="3">
+        <v>48226</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="C48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F36" s="8">
+      <c r="E48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="3">
         <v>90026</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F49" s="3">
+        <v>10012</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="3">
+        <v>33132</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F37" s="8">
-        <v>78741</v>
-      </c>
-      <c r="G37" s="8" t="s">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H37" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F38" s="8">
-        <v>90046</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="B73" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="8">
-        <v>60616</v>
-      </c>
-      <c r="G39" s="8" t="s">
+      <c r="C73" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H39" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="B74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="B75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="B76" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
+      <c r="B77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="B78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
+      <c r="B79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+      <c r="C80" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J19:J29">
-    <sortCondition ref="J19:J29"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J19:J33">
+    <sortCondition ref="J19:J33"/>
   </sortState>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
